--- a/RAMON FRANCO/Septiembre/GASTOS_RAMON FRANCO_Septiembre.xlsx
+++ b/RAMON FRANCO/Septiembre/GASTOS_RAMON FRANCO_Septiembre.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\RAMON FRANCO\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52F25CC-E26D-47FE-94EB-6B45AFE76F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8372AD85-8063-457E-B9BB-C54B8F54B3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$66</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -165,9 +165,6 @@
     <t>subidos JULI de 2025</t>
   </si>
   <si>
-    <t>Matias Salvatierra - Cuota 2 destapacion</t>
-  </si>
-  <si>
     <t>SEÑORES PROPIETARIOS E INQUILINOS: QUIEN NO ABONE EDESUR PAGARA CON PUNITORIOS AL MES SIGUIENTE. LA CAJA MOSTRADA NO ES LA REAL DEBIDO A QUE DENTRO DE LA MISMA SE SOSTIENEN LOS DEUDORES DE EDESUR Y NO SE PUEDEN AVANZAR EN MEJORAS.</t>
   </si>
   <si>
@@ -181,6 +178,12 @@
   </si>
   <si>
     <t>Administraciòn SEPTIEMBRE 2025:</t>
+  </si>
+  <si>
+    <t>Reparacion de sombrero - A.C - Zingueria en terraza -  Reparacion de canaleta - Bajada techo Dpto. - Sellado de grietas en la finalizacion de la canaleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adelanto compra y colocacion semaforo </t>
   </si>
 </sst>
 </file>
@@ -483,7 +486,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -504,15 +507,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -543,7 +540,6 @@
     </xf>
     <xf numFmtId="44" fontId="12" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="6" fontId="8" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -556,11 +552,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="6" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -659,11 +653,17 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="8" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1001,17 +1001,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1021,7 +1021,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="D2" s="13" t="s">
         <v>0</v>
@@ -1031,18 +1031,18 @@
       </c>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="68">
+      <c r="E3" s="59">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="68"/>
+      <c r="F3" s="59"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="D4" s="13" t="s">
         <v>2</v>
@@ -1052,18 +1052,18 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="42" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>3</v>
       </c>
@@ -1071,13 +1071,13 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1087,7 +1087,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1115,435 +1115,436 @@
       <c r="G11" s="2"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="78" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20"/>
-    </row>
-    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="86"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="87"/>
+    </row>
+    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="60">
-        <f>253420*5%+253420</f>
-        <v>266091</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="C14" s="86"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="95">
+        <f>266091*3%+266091</f>
+        <v>274073.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19" t="s">
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="97">
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="95">
         <v>8379</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="49">
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="89">
         <f>SUM(H13:H15)</f>
-        <v>274470</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="79" t="s">
+        <v>282452.73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="80"/>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="81"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="98">
+      <c r="B18" s="86"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="93">
         <v>145038.43</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="25">
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="91">
         <f>SUM(H18:H18)</f>
         <v>145038.43</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="79" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="81"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="95">
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="93"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="86" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="44">
         <v>7186</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="25">
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="91">
         <f>SUM(H21:H22)</f>
         <v>7186</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="82" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="82"/>
-      <c r="C24" s="82"/>
-      <c r="D24" s="82"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="82"/>
-      <c r="H24" s="82"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="86" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="44">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="92" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="86"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22">
+        <f>SUM(H25:H26)</f>
+        <v>70000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="72"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="43"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="95">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="96">
-        <v>202981</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="24">
-        <v>178200</v>
-      </c>
-      <c r="K27">
-        <v>89897</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="24">
-        <v>12050</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="25">
-        <f>SUM(H25:H28)</f>
-        <v>463231</v>
-      </c>
-      <c r="L29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="81"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
-        <v>11</v>
-      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="56">
+        <v>147500</v>
+      </c>
+      <c r="I30" s="43"/>
+      <c r="K30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="18"/>
       <c r="B31" s="19"/>
-      <c r="C31" s="19" t="s">
-        <v>12</v>
-      </c>
+      <c r="C31" s="19"/>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
       <c r="F31" s="19"/>
       <c r="G31" s="19"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="50"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="s">
+      <c r="H31" s="24"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="72"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="96">
+        <v>53282</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="27">
+        <f>H16+H19+H23+H27+H30+H33</f>
+        <v>705459.15999999992</v>
+      </c>
+      <c r="I34" s="51"/>
+      <c r="K34" s="57"/>
+    </row>
+    <row r="35" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="47"/>
+    </row>
+    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="62"/>
+    </row>
+    <row r="37" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="63"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="65"/>
+    </row>
+    <row r="38" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="65">
-        <v>147500</v>
-      </c>
-      <c r="I32" s="50"/>
-      <c r="K32" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="18"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="30"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="79" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="80"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="81"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="99">
-        <v>53282</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="33">
-        <f>H16+H19+H23+H29+H32+H35</f>
-        <v>1090707.43</v>
-      </c>
-      <c r="I36" s="59"/>
-      <c r="K36" s="66"/>
-    </row>
-    <row r="37" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A37" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="54"/>
-    </row>
-    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="71"/>
-    </row>
-    <row r="39" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="72"/>
-      <c r="B39" s="73"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="74"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="83"/>
-      <c r="B40" s="84"/>
-      <c r="C40" s="84"/>
-      <c r="D40" s="84"/>
-      <c r="E40" s="84"/>
-      <c r="F40" s="84"/>
-      <c r="G40" s="84"/>
-      <c r="H40" s="34"/>
-    </row>
-    <row r="41" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="91"/>
-      <c r="B41" s="92"/>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="34"/>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="85"/>
-      <c r="B42" s="86"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="86"/>
-      <c r="E42" s="86"/>
-      <c r="F42" s="86"/>
-      <c r="G42" s="87"/>
-      <c r="H42" s="34"/>
-    </row>
-    <row r="43" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="88" t="s">
+      <c r="B38" s="75"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="75"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="28">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="82" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="83"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="28">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="76"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="28"/>
+    </row>
+    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="89"/>
-      <c r="C43" s="89"/>
-      <c r="D43" s="89"/>
-      <c r="E43" s="89"/>
-      <c r="F43" s="89"/>
-      <c r="G43" s="90"/>
-      <c r="H43" s="35">
-        <f>SUM(H40:H42)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="80"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="29">
+        <f>SUM(H38:H40)</f>
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+    </row>
+    <row r="43" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="52"/>
+    </row>
+    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
@@ -1552,58 +1553,59 @@
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
       <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="62" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="63"/>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
-      <c r="F45" s="63"/>
-      <c r="G45" s="64"/>
-      <c r="H45" s="61">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="94" t="s">
+      <c r="J44" s="15"/>
+    </row>
+    <row r="45" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="94"/>
-      <c r="C47" s="94"/>
-      <c r="D47" s="94"/>
-      <c r="E47" s="94"/>
-      <c r="F47" s="94"/>
-      <c r="G47" s="94"/>
-      <c r="H47" s="33">
-        <f>+H36+H37</f>
-        <v>1090707.43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="36"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="37"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B45" s="85"/>
+      <c r="C45" s="85"/>
+      <c r="D45" s="85"/>
+      <c r="E45" s="85"/>
+      <c r="F45" s="85"/>
+      <c r="G45" s="85"/>
+      <c r="H45" s="27">
+        <f>+H34+H35</f>
+        <v>705459.15999999992</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="31"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+    </row>
+    <row r="48" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="32">
+        <f>H41</f>
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="19"/>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
@@ -1613,209 +1615,184 @@
       <c r="G49" s="19"/>
       <c r="H49" s="19"/>
     </row>
-    <row r="50" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="38">
-        <f>H43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-    </row>
-    <row r="52" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A52" s="75" t="s">
+    <row r="50" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A50" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="B52" s="76"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
-      <c r="F52" s="76"/>
-      <c r="G52" s="76"/>
-      <c r="H52" s="77"/>
-    </row>
-    <row r="53" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A53" s="39" t="s">
+      <c r="B50" s="67"/>
+      <c r="C50" s="67"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="67"/>
+      <c r="F50" s="67"/>
+      <c r="G50" s="67"/>
+      <c r="H50" s="68"/>
+    </row>
+    <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A51" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B53" s="40"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="46">
-        <v>594244.79983787099</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="41" t="s">
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="40">
+        <v>825879.73876219126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B54" s="42"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="42"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="51">
-        <v>1206620.6889243203</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="41"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="47"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="41" t="s">
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="44">
+        <v>1278402.3537500002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="35"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="41"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="42"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="42"/>
-      <c r="H56" s="47">
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="41">
         <v>-16692</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="41" t="s">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="42"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="43">
-        <f>-(H36+H50)</f>
-        <v>-1090707.43</v>
-      </c>
-      <c r="J57" s="15"/>
-    </row>
-    <row r="58" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A58" s="44" t="s">
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="37">
+        <f>-(H34+H48)</f>
+        <v>-1055459.1599999999</v>
+      </c>
+      <c r="J55" s="15"/>
+    </row>
+    <row r="56" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A56" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B58" s="45"/>
-      <c r="C58" s="45"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="55">
-        <f>SUM(H53:H57)</f>
-        <v>693466.05876219133</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B60" s="67" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="67"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="67"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="67"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B61" s="67"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B62" s="67"/>
-      <c r="C62" s="67"/>
-      <c r="D62" s="67"/>
-      <c r="E62" s="67"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="67"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B63" s="67"/>
-      <c r="C63" s="67"/>
-      <c r="D63" s="67"/>
-      <c r="E63" s="67"/>
-      <c r="F63" s="67"/>
-      <c r="G63" s="67"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B64" s="67"/>
-      <c r="C64" s="67"/>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B65" s="67"/>
-      <c r="C65" s="67"/>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B66" s="67"/>
-      <c r="C66" s="67"/>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="67"/>
-      <c r="C67" s="67"/>
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
+      <c r="B56" s="39"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="39"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="48">
+        <f>SUM(H51:H55)</f>
+        <v>1032130.9325121914</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="58"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="58"/>
+      <c r="G59" s="58"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="58"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="58"/>
+      <c r="C61" s="58"/>
+      <c r="D61" s="58"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="58"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="58"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="58"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="58"/>
+      <c r="C64" s="58"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="58"/>
+      <c r="F64" s="58"/>
+      <c r="G64" s="58"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="58"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B60:G67"/>
+    <mergeCell ref="B58:G65"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A38:H39"/>
-    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A36:H37"/>
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
